--- a/docs/evidence/20261024_CoreWeave10Q_計價錨點/CoreWeave10Q_錨點.xlsx
+++ b/docs/evidence/20261024_CoreWeave10Q_計價錨點/CoreWeave10Q_錨點.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="85">
   <si>
     <r>
       <rPr>
@@ -84,18 +84,18 @@
   <si>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">A. Q2 </t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -103,10 +103,10 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">active GW</t>
@@ -280,7 +280,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月新增計半季、</t>
+      <t xml:space="preserve">月新增平均在季內 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2/3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">季、</t>
     </r>
     <r>
       <rPr>
@@ -299,7 +318,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月新增計 </t>
+      <t xml:space="preserve">月新增 </t>
     </r>
     <r>
       <rPr>
@@ -324,18 +343,18 @@
   <si>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">B. </t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -343,18 +362,18 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">active GW </t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -362,18 +381,18 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">$B/GW·</t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -550,7 +569,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">PUE 1.4</t>
+      <t xml:space="preserve">PUE 1.3</t>
     </r>
     <r>
       <rPr>
@@ -565,18 +584,77 @@
   <si>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">口徑 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月漲價（若漲價前即為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">價格）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">C. ÷ TK </t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -584,18 +662,18 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">GB200</t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -603,18 +681,18 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">GB300</t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -736,7 +814,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">PUE 1.4</t>
+      <t xml:space="preserve">PUE 1.3</t>
     </r>
     <r>
       <rPr>
@@ -768,26 +846,185 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">最小</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最大</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IT × </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">漲價、線性</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IT × </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">漲價、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月集中</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">最小（不含漲價列）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最大（不含漲價列）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">區間 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月漲價 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（全部口徑）：最小</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">區間 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月漲價 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（全部口徑）：最大</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">D. </t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -837,28 +1074,103 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">隱含平均耐用年限</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年；對照 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TK IF_DeprLifeIT 6</t>
-    </r>
+    <t xml:space="preserve">隱含平均耐用年限（簡單平均）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年；資產基礎混有資料中心設備、軟體、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年期基礎設施</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">界線：期末基礎 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ Q2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年化折舊</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">年；上界</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">界線：期初基礎 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ H1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年化折舊</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">年；下界</t>
   </si>
   <si>
     <t xml:space="preserve">項目</t>
@@ -1155,6 +1467,560 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Verified</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8-K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8-K 2026-08-11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Expanded active power by nearly 500 MWs to reach 1.5 GW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">其中 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月新增</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">報導（二手）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同上「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt;300MW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">持有成本 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AL_HoldGen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$B/GW·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Derived</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TK v21.2 Alloc!D39</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">持有成本 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AL_HoldGen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TK v21.2 Alloc!E39</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PUE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">低（若 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">active power </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為設施電力）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">區間 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.2–1.4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PUE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">高</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設施係數區間 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Interface </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-07 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">全 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SKU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">漲價</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">報導（法說摘要，二手）</t>
   </si>
   <si>
@@ -1166,26 +2032,322 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MarketBeat 2026-08-11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">「近 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">500MW</t>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">G10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-07 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">全 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SKU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">約漲 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收為漲價前</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">技術設備等折舊資產毛額 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025-12-31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PP&amp;E </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">毛額 − 在建）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">附註 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">33,941 − 9,376</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同上 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-06-30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">附註 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">52,622 − 11,918</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H1 2026 PP&amp;E </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">折舊攤銷</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">附註 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$2.5 billion</t>
     </r>
     <r>
       <rPr>
@@ -1202,366 +2364,20 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">其中 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月新增</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">報導（二手）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">同上「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&gt;300MW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">」</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TK </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">持有成本 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GB200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AL_HoldGen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$B/GW·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Derived</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TK v21.2 Alloc!D39</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TK </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">持有成本 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GB300</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AL_HoldGen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TK v21.2 Alloc!E39</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PUE </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">低（若 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">active power </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">為設施電力）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumed</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">區間 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.2–1.4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PUE </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">高</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">技術設備等折舊資產毛額 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025-12-31</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PP&amp;E </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">毛額 − 在建）</t>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q2 2026 PP&amp;E </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">折舊攤銷</t>
     </r>
   </si>
   <si>
@@ -1591,128 +2407,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">33,941 − 9,376</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">同上 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-06-30</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">附註 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">52,622 − 11,918</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H1 2026 PP&amp;E </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">折舊攤銷</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">附註 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">「</t>
     </r>
     <r>
@@ -1723,16 +2417,16 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">$2.5 billion</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">」</t>
+      <t xml:space="preserve">$1.4 billion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」（四捨五入）</t>
     </r>
   </si>
   <si>
@@ -1827,7 +2521,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1855,13 +2549,6 @@
       <color theme="1"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1919,12 +2606,8 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1940,11 +2623,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2140,7 +2823,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -2152,13 +2835,13 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2166,11 +2849,11 @@
       <c r="A4" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="2" t="n">
         <f aca="false">輸入!$B$4-輸入!$B$5</f>
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2178,11 +2861,11 @@
       <c r="A5" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="2" t="n">
         <f aca="false">(B4+輸入!$B$4)/2</f>
         <v>1.25</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2190,22 +2873,22 @@
       <c r="A6" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="n">
-        <f aca="false">B4+(輸入!$B$5-輸入!$B$6)*0.5+輸入!$B$6*(1/6)</f>
-        <v>1.15</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="B6" s="2" t="n">
+        <f aca="false">B4+(輸入!$B$5-輸入!$B$6)*(2/3)+輸入!$B$6*(1/6)</f>
+        <v>1.18333333333333</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="0" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2213,155 +2896,236 @@
       <c r="A9" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="2" t="n">
         <f aca="false">輸入!$B$2*4/B5</f>
         <v>8.24</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="2" t="n">
         <f aca="false">輸入!$B$2*4/B6</f>
-        <v>8.95652173913043</v>
+        <v>8.70422535211268</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="2" t="n">
         <f aca="false">B9*輸入!$B$9</f>
         <v>9.888</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="2" t="n">
         <f aca="false">C9*輸入!$B$9</f>
-        <v>10.7478260869565</v>
+        <v>10.4450704225352</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="2" t="n">
         <f aca="false">B9*輸入!$B$10</f>
-        <v>11.536</v>
-      </c>
-      <c r="C11" s="3" t="n">
+        <v>10.712</v>
+      </c>
+      <c r="C11" s="2" t="n">
         <f aca="false">C9*輸入!$B$10</f>
-        <v>12.5391304347826</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+        <v>11.3154929577465</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>18</v>
+      <c r="B12" s="2" t="n">
+        <f aca="false">B9*輸入!$B$11</f>
+        <v>10.3</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <f aca="false">C9*輸入!$B$11</f>
+        <v>10.8802816901408</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="0" t="s">
         <v>19</v>
-      </c>
-      <c r="B14" s="3" t="n">
-        <f aca="false">B9/輸入!$B$7</f>
-        <v>0.933376242032096</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <f aca="false">B9/輸入!$B$8</f>
-        <v>0.756906936400146</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="2" t="n">
+        <f aca="false">B9/輸入!$B$7</f>
+        <v>0.933376242032096</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <f aca="false">B9/輸入!$B$8</f>
+        <v>0.756906936400146</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="2" t="n">
         <f aca="false">C9/輸入!$B$7</f>
-        <v>1.01453939351315</v>
-      </c>
-      <c r="C15" s="3" t="n">
+        <v>0.985960819047989</v>
+      </c>
+      <c r="C16" s="2" t="n">
         <f aca="false">C9/輸入!$B$8</f>
-        <v>0.822724930869724</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="3" t="n">
+        <v>0.79954958070438</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="2" t="n">
         <f aca="false">B10/輸入!$B$7</f>
         <v>1.12005149043852</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C17" s="2" t="n">
         <f aca="false">B10/輸入!$B$8</f>
         <v>0.908288323680175</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="3" t="n">
+    <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="2" t="n">
         <f aca="false">C11/輸入!$B$7</f>
-        <v>1.42035515091841</v>
-      </c>
-      <c r="C17" s="3" t="n">
+        <v>1.28174906476239</v>
+      </c>
+      <c r="C18" s="2" t="n">
         <f aca="false">C11/輸入!$B$8</f>
-        <v>1.15181490321761</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="3" t="n">
-        <f aca="false">MIN(B14:C17)</f>
+        <v>1.03941445491569</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <f aca="false">B12/輸入!$B$7</f>
+        <v>1.16672030254012</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <f aca="false">B12/輸入!$B$8</f>
+        <v>0.946133670500183</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <f aca="false">C12/輸入!$B$7</f>
+        <v>1.23245102380999</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <f aca="false">C12/輸入!$B$8</f>
+        <v>0.999436975880475</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <f aca="false">MIN(B15:C18)</f>
         <v>0.756906936400146</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="3" t="n">
-        <f aca="false">MAX(B14:C17)</f>
-        <v>1.42035515091841</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="2" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <f aca="false">MAX(B15:C18)</f>
+        <v>1.28174906476239</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <f aca="false">B21*輸入!$B$11</f>
+        <v>0.946133670500183</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <f aca="false">B22*輸入!$B$11</f>
+        <v>1.60218633095298</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="3" t="n">
-        <f aca="false">(輸入!$B$11+輸入!$B$12)/2</f>
+    <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <f aca="false">(輸入!$B$12+輸入!$B$13)/2</f>
         <v>32.6345</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="3" t="n">
-        <f aca="false">B22/(輸入!$B$13*2)</f>
+      <c r="C27" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <f aca="false">B27/(輸入!$B$14*2)</f>
         <v>6.5269</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>29</v>
+      <c r="C28" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <f aca="false">輸入!$B$13/(輸入!$B$15*4)</f>
+        <v>7.26857142857143</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <f aca="false">輸入!$B$12/(輸入!$B$14*2)</f>
+        <v>4.913</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2380,7 +3144,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -2388,238 +3152,275 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>33</v>
+      <c r="C1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B2" s="5" t="n">
         <v>2.575</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>37</v>
+      <c r="C2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="B3" s="5" t="n">
         <v>4.653</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>40</v>
+      <c r="C3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>43</v>
+      <c r="D4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B5" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>46</v>
+      <c r="D5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="6" t="n">
+      <c r="A6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>49</v>
+      <c r="D6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="B7" s="5" t="n">
         <v>8.82816556596761</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>53</v>
+      <c r="C7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B8" s="5" t="n">
         <v>10.8864110021101</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>55</v>
+      <c r="C8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="B9" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>59</v>
+      <c r="C9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>58</v>
+        <v>69</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="6" t="n">
+      <c r="A11" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="5" t="n">
         <v>24.565</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="6" t="n">
+      <c r="C12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="5" t="n">
         <v>40.704</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>66</v>
+      <c r="C13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="B14" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>69</v>
+      <c r="C16" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
